--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterPropData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterPropData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B768B3-9603-4A24-A5E7-667EA89B3F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFD076-B3FF-46D1-B5B4-929DC8D001A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="1060" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5360" yWindow="2450" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -72,9 +72,6 @@
     <t>默认值</t>
   </si>
   <si>
-    <t>EnumsText+Coin</t>
-  </si>
-  <si>
     <t>UIText+GameGold</t>
   </si>
   <si>
@@ -85,6 +82,13 @@
   </si>
   <si>
     <t>好感值</t>
+  </si>
+  <si>
+    <t>好感度等级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感等级</t>
   </si>
 </sst>
 </file>
@@ -492,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>6</v>
@@ -523,13 +527,13 @@
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -537,15 +541,29 @@
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="E6" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterPropData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterPropData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFD076-B3FF-46D1-B5B4-929DC8D001A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AA2F5A-2961-44EE-8251-84D4753C1606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="2450" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.3">
